--- a/TESTS/zlit_7_aivenko.xlsx
+++ b/TESTS/zlit_7_aivenko.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Вальтер Скотт — шотландський письменник засновник жанру історичного роману</t>
+          <t>Вальтер Скотт</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Англію XII ст. часів короля Ричарда I Левове Серце — протистояння норманів і саксів</t>
+          <t>Англію XII ст. часів короля Ричарда I Левове Серце</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Один з перших класичних зразків історичного роману — поєднав реальну епоху з вигаданими героями</t>
+          <t>Один з перших класичних зразків історичного роману</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Вілфред Айвенго — сакс що повернувся з хрестового походу знеславлений батьком і закоханий у Леді Ровену</t>
+          <t>Вілфред Айвенго</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Між норманами-завойовниками і саксами-підкореними — і боротьба за відновлення справедливості і єдності</t>
+          <t>Між норманами-завойовниками і саксами-підкореними</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Айвенго закохався у Ровену проти волі батька і пішов у хрестовий похід — батько вважав це зрадою роду</t>
+          <t>Айвенго закохався у Ровену проти волі батька і пішов у хрестовий похід</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Таємний лучник і захисник пригноблених — пізніше виявляється що це сам король Ричард I в disguise</t>
+          <t>Таємний лучник і захисник пригноблених</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Єврейська дівчина донька лікаря Ісаака — благородна лікує Айвенго і ледь не загинула на суді за відьомство</t>
+          <t>Єврейська дівчина донька лікаря Ісаака</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Протистояння між соціальним обов'язком (Ровена — своя) і щирою вдячністю (Ревека — чужа але шляхетна)</t>
+          <t>Протистояння між соціальним обов'язком (Ровена</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Під яким іменем таємно з'явився на турнірі в Ашбі повернений з хрестового походу Айвенго?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Під власним ім'ям одразу</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Як «Позбавлений спадщини Лицар», не відкриваючи обличчя</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Як норманський барон</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Як слуга</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Кого переміг загадковий лицар на турнірі в Ашбі, вразивши глядачів?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Короля Ричарда</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кількох найкращих норманських лицарів, включно з Буагільбером</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Локслі</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сера Седріка</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Кому переможець турніру присудив звання «королеви любові і краси»?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ревеці</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Леді Ровені — своїй коханій</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Королеві</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нікому</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Хто такий Седрик і яким він є за переконаннями?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Норманський лорд</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Батько Айвенго, гордий сакс, що не визнає норманської влади</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Друг Буагільбера</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Священник</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Як Седрик ставився до сина через його кохання до Ровени та службу Ричарду?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Підтримував повністю</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Розгнівався і відрікся від нього, бо мав інші плани щодо Ровени</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Йому було байдуже</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він пишався ним публічно</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Що сталося, коли Седрик і його гості зупинились на ніч під час мандрівки?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Все минуло спокійно</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Їх захопили в полон норманські лицарі на чолі з Буагільбером і Фрон де Бефом</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони повернулись додому</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Їх захистив король</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>До якого замку норманські лицарі привезли захоплених полонених — Седрика, Ровену, Ревеку та пораненого Айвенго?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>До свого власного</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>До замку Торкілстон, що належав Фрон де Бефу</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>До королівського палацу</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>До монастиря</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Хто організував напад на замок Торкілстон, щоб звільнити полонених?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сам король Ричард відкрито</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Локслі (Робін Гуд) разом із вільними стрільцями та таємничим чорним лицарем</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Армія короля</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Місцеві селяни самі</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що сталося із замком Торкілстон у фіналі облоги?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він залишився неушкодженим</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Замок згорів у пожежі під час бою, а Фрон де Беф загинув</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Замок здали без бою</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Замок переходить до Седрика</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Хто доглядав за раненим Айвенго в замку Торкілстон під час облоги?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ровена</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ревека, яка лікувала його рани й описувала йому хід бою з вікна</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Седрик</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сама Ревека воювала</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Як Буагільбер ставився до Ревеки під час полону в замку?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Байдуже</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він був зачарований нею і пропонував їй своє кохання й захист, попри різницю релігій</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він її ненавидів</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він її звільнив одразу</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що Буагільбер зробив з Ревекою, коли замок почав горіти?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишив її</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вивіз її з палаючого замку проти її волі, до командорства тамплієрів</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Здав її ворогам</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Загинув разом з нею</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>У чому тамплієри звинуватили Ревеку, коли вона опинилась у їхньому командорстві?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У крадіжці</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У чаклунстві — нібито вона «зачарувала» Буагільбера своєю красою</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У шпигунстві</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У вбивстві</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Яке покарання загрожувало Ревеці за звинуваченням у чаклунстві?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вигнання</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спалення на вогнищі, якщо не знайдеться лицар, готовий захистити її честь у бою</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Тюремне ув'язнення</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Штраф</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Хто погодився стати захисником Ревеки на суді честі, попри власну слабкість після ран?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Седрик</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Айвенго, ледь оговтавшись від ран, з'явився як її захисник</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Локслі</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Король Ричард особисто</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Проти кого Айвенго мав боротися в поєдинку честі за Ревеку?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Проти Фрон де Бефа (вже мертвого)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Проти самого Буагільбера — обвинувача й судового бійця ордену</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Проти Седрика</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Проти короля</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Яким був стан Айвенго перед поєдинком з Буагільбером?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Повністю здоровий</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ще слабкий і не оговтався після ран, але вирішив боротися заради Ревеки</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він відмовився боротися</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він був озброєний краще за супротивника</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Чим закінчився поєдинок Айвенго проти Буагільбера?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Айвенго загинув</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Буагільбер, вражений раптовою появою короля Ричарда серед глядачів, утратив зосередженість і впав мертвим без удару</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поєдинок скасували</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Обидва відмовились боротись</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Хто насправді переховувався під виглядом «Чорного Лицаря», що допомагав звільняти полонених?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Локслі</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сам король Ричард Левове Серце, що повернувся таємно з хрестового походу</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Седрик</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Буагільбер</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Що сталося з Ревекою наприкінці роману?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона залишилась при дворі Ричарда</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона і її батько покинули Англію через переслідування євреїв, попри подяку Айвенго та Ровени</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона вийшла заміж за Айвенго</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона загинула</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Чим закінчується роман «Айвенго» для головного героя?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він гине у бою</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він одружується з Ровеною, отримавши прощення батька і визнання короля Ричарда</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він стає монахом</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він залишається самотнім</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що таке «історичний роман» як жанр і яку роль відіграв Скотт у його становленні?</t>
+          <t>Вальтер Скотт вважається одним із засновників жанру історичного роману у європейській літературі.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє король Ричард I у сюжеті «Айвенго»?</t>
+          <t>Король Ричард I у романі діє відкрито від початку, а не таємно під виглядом Чорного Лицаря.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яке значення «Айвенго» для розуміння середньовічного суспільства?</t>
+          <t>«Айвенго» допомагає зрозуміти суспільні протиріччя середньовічної Англії — між норманами і саксами, лицарями і простолюдом, християнами і євреями.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея роману «Айвенго»?</t>
+          <t>Головна ідея «Айвенго» — справжня шляхетність визначається вчинками й характером, а не походженням.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Що символізує образ Ревеки у романі?</t>
+          <t>Образ Ревеки символізує шляхетність і гідність людини, що зазнає упереджень через своє походження.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яку думку про лицарство виражає Вальтер Скотт через роман?</t>
+          <t>Через образи Буагільбера і Седрика Скотт стверджує, що лицарський ідеал завжди відповідає реальній поведінці лицарів.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які теми розкриває роман «Айвенго»?</t>
+          <t>Що сталося в романі «Айвенго»?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Протистояння норманів і саксів</t>
+          <t>Захоплених полонених звільнили при облозі Торкілстона</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Шляхетність незалежно від походження</t>
+          <t>Ревеку звинуватили в чаклунстві</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Любов до середньовічної зброї</t>
+          <t>Буагільбер виграв поєдинок проти Айвенго</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Справедливість і відновлення закону</t>
+          <t>Король Ричард діяв таємно як Чорний Лицар</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ключовий сюжетний вузол — Айвенго бере участь таємно перемагає норманів але отримує важке поранення</t>
+          <t>Ключовий сюжетний вузол</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Норманський рицар-тамплієр — антагоніст що захоплений Ревекою але стоїть на боці несправедливості</t>
+          <t>Норманський рицар-тамплієр</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Він гине в поєдинку проти Айвенго який виступив захисником Ревеки — загинув від внутрішнього конфлікту</t>
+          <t>Він гине в поєдинку проти Айвенго який виступив захисником Ревеки</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
